--- a/regno.xlsx.xlsx
+++ b/regno.xlsx.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9114f0d97d67d985/Desktop/git demo/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D06EABCA-7E8D-40A7-B9EC-470F60A2B30F}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{921ECD1B-E566-4BD9-AD03-15B8ED5BFBEB}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -245,6 +245,24 @@
   </si>
   <si>
     <t>had a nice weekend</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>Very Unsatisfied</t>
+  </si>
+  <si>
+    <t>got sick today</t>
+  </si>
+  <si>
+    <t>I studied very well today</t>
+  </si>
+  <si>
+    <t>garv saini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mca  </t>
   </si>
 </sst>
 </file>
@@ -931,20 +949,26 @@
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="20"/>
+      <c r="B2" s="20" t="s">
+        <v>77</v>
+      </c>
       <c r="C2" s="20"/>
       <c r="D2" s="20"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="20"/>
+      <c r="F2" s="20">
+        <v>12624955</v>
+      </c>
       <c r="G2" s="20"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="20"/>
+      <c r="B3" s="20" t="s">
+        <v>78</v>
+      </c>
       <c r="C3" s="20"/>
       <c r="D3" s="20"/>
       <c r="E3" s="6" t="s">
@@ -1936,180 +1960,372 @@
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+      <c r="A26" s="13">
+        <v>46279</v>
+      </c>
+      <c r="B26" s="14">
+        <v>360</v>
+      </c>
+      <c r="C26" s="14">
+        <v>60</v>
+      </c>
+      <c r="D26" s="14">
+        <v>180</v>
+      </c>
+      <c r="E26" s="14">
+        <v>60</v>
+      </c>
+      <c r="F26" s="14">
+        <v>250</v>
+      </c>
+      <c r="G26" s="14">
+        <v>5</v>
+      </c>
+      <c r="H26" s="14">
+        <v>100</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>1010</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
+        <v>430</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+      <c r="A27" s="13">
+        <v>46280</v>
+      </c>
+      <c r="B27" s="14">
+        <v>360</v>
+      </c>
+      <c r="C27" s="14">
+        <v>60</v>
+      </c>
+      <c r="D27" s="14">
+        <v>200</v>
+      </c>
+      <c r="E27" s="14">
+        <v>50</v>
+      </c>
+      <c r="F27" s="14">
+        <v>150</v>
+      </c>
+      <c r="G27" s="14">
+        <v>3</v>
+      </c>
+      <c r="H27" s="14">
+        <v>60</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>880</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
+        <v>560</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+      <c r="A28" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B28" s="14">
+        <v>300</v>
+      </c>
+      <c r="C28" s="14">
+        <v>60</v>
+      </c>
+      <c r="D28" s="14">
+        <v>180</v>
+      </c>
+      <c r="E28" s="14">
+        <v>60</v>
+      </c>
+      <c r="F28" s="14">
+        <v>400</v>
+      </c>
+      <c r="G28" s="14">
+        <v>8</v>
+      </c>
+      <c r="H28" s="14">
+        <v>60</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
+        <v>380</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+      <c r="A29" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B29" s="14">
+        <v>360</v>
+      </c>
+      <c r="C29" s="14">
+        <v>60</v>
+      </c>
+      <c r="D29" s="14">
+        <v>120</v>
+      </c>
+      <c r="E29" s="14">
+        <v>45</v>
+      </c>
+      <c r="F29" s="14">
+        <v>200</v>
+      </c>
+      <c r="G29" s="14">
+        <v>4</v>
+      </c>
+      <c r="H29" s="14">
+        <v>100</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>885</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
+        <v>555</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+      <c r="A30" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B30" s="14">
+        <v>300</v>
+      </c>
+      <c r="C30" s="14">
+        <v>60</v>
+      </c>
+      <c r="D30" s="14">
+        <v>90</v>
+      </c>
+      <c r="E30" s="14">
+        <v>0</v>
+      </c>
+      <c r="F30" s="14">
+        <v>250</v>
+      </c>
+      <c r="G30" s="14">
+        <v>5</v>
+      </c>
+      <c r="H30" s="14">
+        <v>180</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>880</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
+        <v>560</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+      <c r="A31" s="13">
+        <v>46284</v>
+      </c>
+      <c r="B31" s="14">
+        <v>420</v>
+      </c>
+      <c r="C31" s="14">
+        <v>120</v>
+      </c>
+      <c r="D31" s="14">
+        <v>240</v>
+      </c>
+      <c r="E31" s="14">
+        <v>100</v>
+      </c>
+      <c r="F31" s="14">
+        <v>0</v>
+      </c>
+      <c r="G31" s="14">
+        <v>0</v>
+      </c>
+      <c r="H31" s="14">
+        <v>50</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>930</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
+        <v>510</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+      <c r="A32" s="13">
+        <v>46285</v>
+      </c>
+      <c r="B32" s="14">
+        <v>420</v>
+      </c>
+      <c r="C32" s="14">
+        <v>150</v>
+      </c>
+      <c r="D32" s="14">
+        <v>300</v>
+      </c>
+      <c r="E32" s="14">
+        <v>120</v>
+      </c>
+      <c r="F32" s="14">
+        <v>0</v>
+      </c>
+      <c r="G32" s="14">
+        <v>0</v>
+      </c>
+      <c r="H32" s="14">
+        <v>60</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="17"/>
+        <v>390</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N32" s="17" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+      <c r="A33" s="13">
+        <v>46286</v>
+      </c>
+      <c r="B33" s="14">
+        <v>360</v>
+      </c>
+      <c r="C33" s="14">
+        <v>60</v>
+      </c>
+      <c r="D33" s="14">
+        <v>120</v>
+      </c>
+      <c r="E33" s="14">
+        <v>60</v>
+      </c>
+      <c r="F33" s="14">
+        <v>250</v>
+      </c>
+      <c r="G33" s="14">
+        <v>5</v>
+      </c>
+      <c r="H33" s="14">
+        <v>90</v>
+      </c>
+      <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>940</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="17"/>
+        <v>500</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N33" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="13"/>
